--- a/application/plugins/StockSectorManager/views/stockBill.xlsx
+++ b/application/plugins/StockSectorManager/views/stockBill.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Wamp.NET\sites\isell\isell\application\plugins\StockSectorManager\views\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
@@ -105,11 +110,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;\-0;\-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -164,6 +169,14 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -225,9 +238,6 @@
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -247,44 +257,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -292,18 +311,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -379,14 +392,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -424,9 +440,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -461,7 +477,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -496,7 +512,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -682,86 +698,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="25" t="s">
@@ -773,74 +789,74 @@
       <c r="G6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11" t="s">
+      <c r="E8" s="19"/>
+      <c r="F8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/application/plugins/StockSectorManager/views/stockBill.xlsx
+++ b/application/plugins/StockSectorManager/views/stockBill.xlsx
@@ -114,7 +114,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0;\-0;\-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -169,14 +169,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -311,7 +303,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
